--- a/Result/profitability/3630.xlsx
+++ b/Result/profitability/3630.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002500000000000013</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>8.90875</v>
+        <v>10.865</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.82</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2075</v>
+        <v>0.23875</v>
       </c>
       <c r="N3" t="n">
-        <v>12.58625</v>
+        <v>14.2225</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2775</v>
+        <v>0.28875</v>
       </c>
       <c r="N4" t="n">
-        <v>16.24375</v>
+        <v>17.06875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3025</v>
+        <v>-0.14</v>
       </c>
       <c r="N5" t="n">
-        <v>18.22125</v>
+        <v>18.28375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01125000000000002</v>
+        <v>-0.02625000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>19.25125</v>
+        <v>20.65625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.12125</v>
+        <v>0.10125</v>
       </c>
       <c r="N7" t="n">
-        <v>23.4075</v>
+        <v>24.82375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0.225</v>
+        <v>0.19875</v>
       </c>
       <c r="N8" t="n">
-        <v>27.38625</v>
+        <v>27.94125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>603</v>
+      </c>
+      <c r="D74" t="n">
+        <v>509</v>
+      </c>
+      <c r="E74" t="n">
+        <v>94</v>
+      </c>
+      <c r="F74" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-81</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-13.46%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-98</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-98</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-0.06124999999999999</v>
+      </c>
+      <c r="N74" t="n">
+        <v>7.65375</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.4010840108401084</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-1.156862745098039</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0.03331112591605589</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
